--- a/data/Spring2026/Automating-toy-network-file-making-process/Data/Trial 19/Trial_19_output_perm_summary.xlsx
+++ b/data/Spring2026/Automating-toy-network-file-making-process/Data/Trial 19/Trial_19_output_perm_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lmu0-my.sharepoint.com/personal/nchun2_lion_lmu_edu/Documents/Desktop/Research/Spring 2026/Automating Perms/Files/Trial 19/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lmu0-my.sharepoint.com/personal/nchun2_lion_lmu_edu/Documents/Documents/GitHub/DahlquistLabTest/data/Spring2026/Automating-toy-network-file-making-process/Data/Trial 19/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="916" documentId="13_ncr:1_{04452017-E17C-4B8D-AAE6-9AA0DE2B5435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90C21F53-0F36-4B5E-BB7B-11FB7ABBF488}"/>
+  <xr:revisionPtr revIDLastSave="917" documentId="13_ncr:1_{04452017-E17C-4B8D-AAE6-9AA0DE2B5435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B197B603-C614-46E0-850C-1A994912E99A}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="11" r:id="rId1"/>
@@ -130,8 +130,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="173" formatCode="0.000E+00"/>
-    <numFmt numFmtId="174" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
+    <numFmt numFmtId="165" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -610,11 +610,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="348" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="348" applyFont="1" applyFill="1"/>
@@ -975,28 +975,7 @@
     <cellStyle name="Normal 3 2" xfId="350" xr:uid="{15796C32-93EF-4B35-A802-F9E0DA357C31}"/>
     <cellStyle name="Normal 4" xfId="348" xr:uid="{53C50B39-1D83-469D-BBDC-5270904EE3B2}"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1010,24 +989,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1065,27 +1034,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1156,76 +1105,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>19.010000000000002</c:v>
+                  <c:v>19.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.05</c:v>
+                  <c:v>19.14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.09</c:v>
+                  <c:v>19.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.11</c:v>
+                  <c:v>19.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.03</c:v>
+                  <c:v>19.190000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>19.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>19.21</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>19.04</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.190000000000001</c:v>
+                  <c:v>19.149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.100000000000001</c:v>
+                  <c:v>19.16</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.23</c:v>
+                  <c:v>19.239999999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>19.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>19.23</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>19.12</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>19.13</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>19.149999999999999</c:v>
+                <c:pt idx="15">
+                  <c:v>19.09</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>19.059999999999999</c:v>
+                <c:pt idx="16">
+                  <c:v>19.010000000000002</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
+                  <c:v>19.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.03</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.07</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>19.079999999999998</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>19.239999999999998</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19.07</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>19.18</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>19.170000000000002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>19.16</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>19.2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>19.14</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>19.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1237,76 +1186,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>2.0881437090631762E-12</c:v>
+                  <c:v>2.3332018733578362E-7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0881437090631762E-12</c:v>
+                  <c:v>1.4199345186229222E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.0881440918891168E-12</c:v>
+                  <c:v>1.0312979041528754E-10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5539762344854189E-12</c:v>
+                  <c:v>1.4199757995948576E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.5539783829298557E-12</c:v>
+                  <c:v>2.0477010436286962E-10</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>2.0477021575589668E-10</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1.0312977635369039E-10</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.0312979041528754E-10</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.0477010436286962E-10</c:v>
+                  <c:v>4.7249992214528933E-10</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.0477021575589668E-10</c:v>
+                  <c:v>2.3331988787638911E-7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5180763563260601E-10</c:v>
+                  <c:v>6.4617952305259628E-10</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.5180775969235166E-10</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2.5180763563260601E-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.72499948167661E-10</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>2.6519440572611286E-10</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>2.6519442271199434E-10</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.7249992214528933E-10</c:v>
+                <c:pt idx="15">
+                  <c:v>2.0881440918891168E-12</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.72499948167661E-10</c:v>
+                <c:pt idx="16">
+                  <c:v>2.0881437090631762E-12</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
+                  <c:v>2.0881437090631762E-12</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5539783829298557E-12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.5539762344854189E-12</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.6319783255222926E-8</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>6.4617947087495634E-10</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4617952305259628E-10</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.6319783255222926E-8</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>2.6319800010841316E-8</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>4.0626556311774439E-8</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2.3331988787638911E-7</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2.3332018733578362E-7</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.4199345186229222E-6</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1.4199757995948576E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1339,76 +1288,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>19.010000000000002</c:v>
+                  <c:v>19.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.05</c:v>
+                  <c:v>19.14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.09</c:v>
+                  <c:v>19.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.11</c:v>
+                  <c:v>19.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.03</c:v>
+                  <c:v>19.190000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>19.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>19.21</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>19.04</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.190000000000001</c:v>
+                  <c:v>19.149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.100000000000001</c:v>
+                  <c:v>19.16</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.23</c:v>
+                  <c:v>19.239999999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>19.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>19.23</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>19.12</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>19.13</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>19.149999999999999</c:v>
+                <c:pt idx="15">
+                  <c:v>19.09</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>19.059999999999999</c:v>
+                <c:pt idx="16">
+                  <c:v>19.010000000000002</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
+                  <c:v>19.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.03</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.07</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>19.079999999999998</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>19.239999999999998</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19.07</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>19.18</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>19.170000000000002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>19.16</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>19.2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>19.14</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>19.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1420,76 +1369,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>1.9470856808913606</c:v>
+                  <c:v>5.1527152796674733E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9470856808913606</c:v>
+                  <c:v>0.15400575172517667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6943949993127694</c:v>
+                  <c:v>0.17345373290931654</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7223037365615141</c:v>
+                  <c:v>0.18769071637266901</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.5811204248726205</c:v>
+                  <c:v>0.23182367907598339</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0.29665338239151751</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.33920256626643935</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.17345373290931654</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.23182367907598339</c:v>
+                  <c:v>0.34260860307780583</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.29665338239151751</c:v>
+                  <c:v>0.34870634675575252</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.83138010914364335</c:v>
+                  <c:v>0.62062569880872542</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.82711497453429728</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0.83138010914364335</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.9199480086205134</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.0344397810141184</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>1.0394427441154028</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.34260860307780583</c:v>
+                <c:pt idx="15">
+                  <c:v>1.6943949993127694</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.9199480086205134</c:v>
+                <c:pt idx="16">
+                  <c:v>1.9470856808913606</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
+                  <c:v>1.9470856808913606</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5811204248726205</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.7223037365615141</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.0329403694450945</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>3.9638656453899062</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.62062569880872542</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3.0329403694450945</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>4.3882642742190328</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>4.4820954895710683</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.34870634675575252</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.1527152796674733E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.15400575172517667</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.18769071637266901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2662,13 +2611,13 @@
         <v>1.9470860274437103</v>
       </c>
       <c r="N2">
-        <v>19.010000000000002</v>
+        <v>19.2</v>
       </c>
       <c r="O2">
-        <v>1.9470856808913606</v>
+        <v>5.1527152796674733E-2</v>
       </c>
       <c r="P2">
-        <v>2.0881437090631762E-12</v>
+        <v>2.3332018733578362E-7</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -2708,13 +2657,13 @@
         <v>1.0765068349821847</v>
       </c>
       <c r="N3">
-        <v>19.05</v>
+        <v>19.14</v>
       </c>
       <c r="O3">
-        <v>1.9470856808913606</v>
+        <v>0.15400575172517667</v>
       </c>
       <c r="P3">
-        <v>2.0881437090631762E-12</v>
+        <v>1.4199345186229222E-6</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -2754,13 +2703,13 @@
         <v>2.5811206851513111</v>
       </c>
       <c r="N4">
-        <v>19.09</v>
+        <v>19.04</v>
       </c>
       <c r="O4">
-        <v>1.6943949993127694</v>
+        <v>0.17345373290931654</v>
       </c>
       <c r="P4">
-        <v>2.0881440918891168E-12</v>
+        <v>1.0312979041528754E-10</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -2800,13 +2749,13 @@
         <v>35.964779261027616</v>
       </c>
       <c r="N5">
-        <v>19.11</v>
+        <v>19.22</v>
       </c>
       <c r="O5">
-        <v>2.7223037365615141</v>
+        <v>0.18769071637266901</v>
       </c>
       <c r="P5">
-        <v>2.5539762344854189E-12</v>
+        <v>1.4199757995948576E-6</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -2834,13 +2783,13 @@
         <v>1.9470860274437103</v>
       </c>
       <c r="N6">
-        <v>19.03</v>
+        <v>19.190000000000001</v>
       </c>
       <c r="O6">
-        <v>2.5811204248726205</v>
+        <v>0.23182367907598339</v>
       </c>
       <c r="P6">
-        <v>2.5539783829298557E-12</v>
+        <v>2.0477010436286962E-10</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -2868,13 +2817,13 @@
         <v>0.92991849395695625</v>
       </c>
       <c r="N7">
-        <v>19.21</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="O7">
-        <v>0.33920256626643935</v>
+        <v>0.29665338239151751</v>
       </c>
       <c r="P7">
-        <v>1.0312977635369039E-10</v>
+        <v>2.0477021575589668E-10</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -2902,13 +2851,13 @@
         <v>3.0334772861195742</v>
       </c>
       <c r="N8">
-        <v>19.04</v>
+        <v>19.21</v>
       </c>
       <c r="O8">
-        <v>0.17345373290931654</v>
+        <v>0.33920256626643935</v>
       </c>
       <c r="P8">
-        <v>1.0312979041528754E-10</v>
+        <v>1.0312977635369039E-10</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -2936,13 +2885,13 @@
         <v>40.02852470115068</v>
       </c>
       <c r="N9">
-        <v>19.190000000000001</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="O9">
-        <v>0.23182367907598339</v>
+        <v>0.34260860307780583</v>
       </c>
       <c r="P9">
-        <v>2.0477010436286962E-10</v>
+        <v>4.7249992214528933E-10</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -2970,13 +2919,13 @@
         <v>1.6943953458648398</v>
       </c>
       <c r="N10">
-        <v>19.100000000000001</v>
+        <v>19.16</v>
       </c>
       <c r="O10">
-        <v>0.29665338239151751</v>
+        <v>0.34870634675575252</v>
       </c>
       <c r="P10">
-        <v>2.0477021575589668E-10</v>
+        <v>2.3331988787638911E-7</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -3004,13 +2953,13 @@
         <v>23.640133129069483</v>
       </c>
       <c r="N11">
-        <v>19.23</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="O11">
-        <v>0.83138010914364335</v>
+        <v>0.62062569880872542</v>
       </c>
       <c r="P11">
-        <v>2.5180763563260601E-10</v>
+        <v>6.4617952305259628E-10</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -3072,13 +3021,13 @@
         <v>27.508381594457386</v>
       </c>
       <c r="N13">
-        <v>19.12</v>
+        <v>19.23</v>
       </c>
       <c r="O13">
-        <v>1.0344397810141184</v>
+        <v>0.83138010914364335</v>
       </c>
       <c r="P13">
-        <v>2.6519440572611286E-10</v>
+        <v>2.5180763563260601E-10</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -3106,13 +3055,13 @@
         <v>12.844421925847975</v>
       </c>
       <c r="N14">
-        <v>19.13</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="O14">
-        <v>1.0394427441154028</v>
+        <v>0.9199480086205134</v>
       </c>
       <c r="P14">
-        <v>2.6519442271199434E-10</v>
+        <v>4.72499948167661E-10</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -3140,13 +3089,13 @@
         <v>0.24483148945459202</v>
       </c>
       <c r="N15">
-        <v>19.149999999999999</v>
+        <v>19.12</v>
       </c>
       <c r="O15">
-        <v>0.34260860307780583</v>
+        <v>1.0344397810141184</v>
       </c>
       <c r="P15">
-        <v>4.7249992214528933E-10</v>
+        <v>2.6519440572611286E-10</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
@@ -3174,13 +3123,13 @@
         <v>0.34278494550019972</v>
       </c>
       <c r="N16">
-        <v>19.059999999999999</v>
+        <v>19.13</v>
       </c>
       <c r="O16">
-        <v>0.9199480086205134</v>
+        <v>1.0394427441154028</v>
       </c>
       <c r="P16">
-        <v>4.72499948167661E-10</v>
+        <v>2.6519442271199434E-10</v>
       </c>
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.3">
@@ -3208,13 +3157,13 @@
         <v>0.42964094070937137</v>
       </c>
       <c r="N17">
-        <v>19.079999999999998</v>
+        <v>19.09</v>
       </c>
       <c r="O17">
-        <v>3.9638656453899062</v>
+        <v>1.6943949993127694</v>
       </c>
       <c r="P17">
-        <v>6.4617947087495634E-10</v>
+        <v>2.0881440918891168E-12</v>
       </c>
       <c r="AB17" s="6">
         <v>-2</v>
@@ -3315,13 +3264,13 @@
         <v>39.076780515338854</v>
       </c>
       <c r="N18">
-        <v>19.239999999999998</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="O18">
-        <v>0.62062569880872542</v>
+        <v>1.9470856808913606</v>
       </c>
       <c r="P18">
-        <v>6.4617952305259628E-10</v>
+        <v>2.0881437090631762E-12</v>
       </c>
       <c r="AB18" s="6">
         <v>-1</v>
@@ -3422,13 +3371,13 @@
         <v>4.3888011804772029</v>
       </c>
       <c r="N19">
-        <v>19.07</v>
+        <v>19.05</v>
       </c>
       <c r="O19">
-        <v>3.0329403694450945</v>
+        <v>1.9470856808913606</v>
       </c>
       <c r="P19">
-        <v>2.6319783255222926E-8</v>
+        <v>2.0881437090631762E-12</v>
       </c>
       <c r="AB19" s="6">
         <v>1</v>
@@ -3529,13 +3478,13 @@
         <v>23.579890642020825</v>
       </c>
       <c r="N20">
-        <v>19.18</v>
+        <v>19.03</v>
       </c>
       <c r="O20">
-        <v>4.3882642742190328</v>
+        <v>2.5811204248726205</v>
       </c>
       <c r="P20">
-        <v>2.6319800010841316E-8</v>
+        <v>2.5539783829298557E-12</v>
       </c>
       <c r="AB20" s="6">
         <v>2</v>
@@ -3636,13 +3585,13 @@
         <v>0.13247030635093371</v>
       </c>
       <c r="N21">
-        <v>19.170000000000002</v>
+        <v>19.11</v>
       </c>
       <c r="O21">
-        <v>4.4820954895710683</v>
+        <v>2.7223037365615141</v>
       </c>
       <c r="P21">
-        <v>4.0626556311774439E-8</v>
+        <v>2.5539762344854189E-12</v>
       </c>
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.3">
@@ -3670,13 +3619,13 @@
         <v>20.142817086258411</v>
       </c>
       <c r="N22">
-        <v>19.16</v>
+        <v>19.07</v>
       </c>
       <c r="O22">
-        <v>0.34870634675575252</v>
+        <v>3.0329403694450945</v>
       </c>
       <c r="P22">
-        <v>2.3331988787638911E-7</v>
+        <v>2.6319783255222926E-8</v>
       </c>
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.3">
@@ -3704,13 +3653,13 @@
         <v>0.27855249496172252</v>
       </c>
       <c r="N23">
-        <v>19.2</v>
+        <v>19.079999999999998</v>
       </c>
       <c r="O23">
-        <v>5.1527152796674733E-2</v>
+        <v>3.9638656453899062</v>
       </c>
       <c r="P23">
-        <v>2.3332018733578362E-7</v>
+        <v>6.4617947087495634E-10</v>
       </c>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.3">
@@ -3738,13 +3687,13 @@
         <v>1.0841922097091896</v>
       </c>
       <c r="N24">
-        <v>19.14</v>
+        <v>19.18</v>
       </c>
       <c r="O24">
-        <v>0.15400575172517667</v>
+        <v>4.3882642742190328</v>
       </c>
       <c r="P24">
-        <v>1.4199345186229222E-6</v>
+        <v>2.6319800010841316E-8</v>
       </c>
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.3">
@@ -3772,13 +3721,13 @@
         <v>34.387306693082579</v>
       </c>
       <c r="N25">
-        <v>19.22</v>
+        <v>19.170000000000002</v>
       </c>
       <c r="O25">
-        <v>0.18769071637266901</v>
+        <v>4.4820954895710683</v>
       </c>
       <c r="P25">
-        <v>1.4199757995948576E-6</v>
+        <v>4.0626556311774439E-8</v>
       </c>
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.3">
@@ -4920,36 +4869,36 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:P25">
-    <sortCondition ref="P2:P25"/>
+    <sortCondition ref="O2:O25"/>
   </sortState>
   <conditionalFormatting sqref="A44:X47">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+      <formula>-1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
+      <formula>-2</formula>
+    </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal">
       <formula>-2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>-2</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB17:AY20">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>-1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
-      <formula>2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB17:AY20">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>-1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>-2</formula>
     </cfRule>
     <cfRule type="cellIs" priority="5" operator="equal">
@@ -25228,7 +25177,7 @@
         <v>1.1102230246251565E-16</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" ref="D32:D33" si="10">(D28-A22)</f>
+        <f t="shared" ref="D32" si="10">(D28-A22)</f>
         <v>1.1102230246251565E-16</v>
       </c>
       <c r="E32" s="4">
@@ -25240,7 +25189,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="4">
-        <f t="shared" ref="G32:G33" si="13">G28-B22</f>
+        <f t="shared" ref="G32" si="13">G28-B22</f>
         <v>0</v>
       </c>
       <c r="H32" s="4">
